--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105530</v>
+        <v>105532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105532</v>
+        <v>105545</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105545</v>
+        <v>105547</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105547</v>
+        <v>105551</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105551</v>
+        <v>105570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105570</v>
+        <v>105571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105571</v>
+        <v>105576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105576</v>
+        <v>105579</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105579</v>
+        <v>105585</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105585</v>
+        <v>105586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105586</v>
+        <v>105598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105598</v>
+        <v>105599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105599</v>
+        <v>105602</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 32530-2023 artfynd.xlsx
+++ b/artfynd/A 32530-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137193032</v>
       </c>
       <c r="B2" t="n">
-        <v>105602</v>
+        <v>105608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
